--- a/Data/PaNET_mapping.xlsx
+++ b/Data/PaNET_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fdp54928/Documents/PaNET-classifier/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03051ECA-D400-E846-8513-28BDB8C14CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6D549B-0BE0-6A4A-8310-41A77B9EBD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{88D9EF37-0CDC-9F43-8BAB-2F9D8923655A}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17380" xr2:uid="{88D9EF37-0CDC-9F43-8BAB-2F9D8923655A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="285">
   <si>
-    <t>PaNET ID</t>
-  </si>
-  <si>
     <t>Diffraction</t>
   </si>
   <si>
@@ -891,6 +888,9 @@
   </si>
   <si>
     <t>Near ambient and ambient pressure XPS seem to be the same thing.</t>
+  </si>
+  <si>
+    <t>PaNET label</t>
   </si>
 </sst>
 </file>
@@ -1272,1099 +1272,1099 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>122</v>
+        <v>284</v>
       </c>
       <c r="D1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
         <v>123</v>
-      </c>
-      <c r="C10" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
         <v>125</v>
-      </c>
-      <c r="C11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
         <v>127</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" t="s">
         <v>129</v>
-      </c>
-      <c r="C14" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" t="s">
         <v>131</v>
-      </c>
-      <c r="C15" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" t="s">
         <v>133</v>
-      </c>
-      <c r="C16" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" t="s">
         <v>135</v>
-      </c>
-      <c r="C17" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" t="s">
         <v>137</v>
-      </c>
-      <c r="C18" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" t="s">
         <v>139</v>
-      </c>
-      <c r="C19" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" t="s">
         <v>141</v>
-      </c>
-      <c r="C20" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" t="s">
         <v>143</v>
-      </c>
-      <c r="C21" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
         <v>145</v>
-      </c>
-      <c r="C22" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" t="s">
         <v>147</v>
-      </c>
-      <c r="C23" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" t="s">
         <v>149</v>
-      </c>
-      <c r="C24" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" t="s">
         <v>151</v>
-      </c>
-      <c r="C25" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
         <v>153</v>
-      </c>
-      <c r="C26" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" t="s">
         <v>155</v>
-      </c>
-      <c r="C30" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" t="s">
         <v>157</v>
-      </c>
-      <c r="C31" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" t="s">
         <v>159</v>
-      </c>
-      <c r="C32" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
         <v>161</v>
-      </c>
-      <c r="C33" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" t="s">
         <v>163</v>
-      </c>
-      <c r="C34" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" t="s">
         <v>165</v>
-      </c>
-      <c r="C35" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
         <v>167</v>
-      </c>
-      <c r="C36" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" t="s">
         <v>169</v>
-      </c>
-      <c r="C37" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" t="s">
         <v>171</v>
-      </c>
-      <c r="C38" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" t="s">
         <v>173</v>
-      </c>
-      <c r="C39" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s">
         <v>175</v>
-      </c>
-      <c r="C40" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" t="s">
         <v>177</v>
-      </c>
-      <c r="C41" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" t="s">
         <v>179</v>
-      </c>
-      <c r="C42" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" t="s">
         <v>181</v>
-      </c>
-      <c r="C43" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" t="s">
         <v>183</v>
-      </c>
-      <c r="C44" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" t="s">
         <v>185</v>
-      </c>
-      <c r="C45" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" t="s">
         <v>187</v>
-      </c>
-      <c r="C46" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" t="s">
         <v>189</v>
-      </c>
-      <c r="C47" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" t="s">
         <v>191</v>
-      </c>
-      <c r="C48" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" t="s">
         <v>193</v>
-      </c>
-      <c r="C51" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" t="s">
         <v>195</v>
-      </c>
-      <c r="C52" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" t="s">
         <v>197</v>
-      </c>
-      <c r="C54" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
+        <v>198</v>
+      </c>
+      <c r="C55" t="s">
         <v>199</v>
-      </c>
-      <c r="C55" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" t="s">
         <v>201</v>
-      </c>
-      <c r="C56" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" t="s">
         <v>203</v>
-      </c>
-      <c r="C57" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C58" t="s">
         <v>205</v>
-      </c>
-      <c r="C58" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" t="s">
         <v>207</v>
-      </c>
-      <c r="C59" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" t="s">
         <v>209</v>
-      </c>
-      <c r="C60" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" t="s">
         <v>211</v>
-      </c>
-      <c r="C61" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
+        <v>212</v>
+      </c>
+      <c r="C62" t="s">
         <v>213</v>
-      </c>
-      <c r="C62" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" t="s">
         <v>215</v>
-      </c>
-      <c r="C63" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" t="s">
         <v>217</v>
-      </c>
-      <c r="C64" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" t="s">
         <v>219</v>
-      </c>
-      <c r="C65" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
+        <v>220</v>
+      </c>
+      <c r="C66" t="s">
         <v>221</v>
-      </c>
-      <c r="C66" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
+        <v>222</v>
+      </c>
+      <c r="C67" t="s">
         <v>223</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>224</v>
-      </c>
-      <c r="D67" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" t="s">
         <v>227</v>
-      </c>
-      <c r="C68" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
+        <v>228</v>
+      </c>
+      <c r="C69" t="s">
         <v>229</v>
-      </c>
-      <c r="C69" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s">
+        <v>230</v>
+      </c>
+      <c r="C70" t="s">
         <v>231</v>
-      </c>
-      <c r="C70" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
+        <v>232</v>
+      </c>
+      <c r="C71" t="s">
         <v>233</v>
-      </c>
-      <c r="C71" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
+        <v>234</v>
+      </c>
+      <c r="C72" t="s">
         <v>235</v>
-      </c>
-      <c r="C72" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" t="s">
         <v>239</v>
-      </c>
-      <c r="C81" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B85" t="s">
+        <v>236</v>
+      </c>
+      <c r="C85" t="s">
         <v>237</v>
-      </c>
-      <c r="C85" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B86" t="s">
+        <v>240</v>
+      </c>
+      <c r="C86" t="s">
         <v>241</v>
-      </c>
-      <c r="C86" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C87" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B88" t="s">
+        <v>244</v>
+      </c>
+      <c r="C88" t="s">
         <v>245</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>246</v>
-      </c>
-      <c r="D88" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B90" t="s">
+        <v>247</v>
+      </c>
+      <c r="C90" t="s">
         <v>248</v>
-      </c>
-      <c r="C90" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B91" t="s">
+        <v>249</v>
+      </c>
+      <c r="C91" t="s">
         <v>250</v>
       </c>
-      <c r="C91" t="s">
-        <v>251</v>
-      </c>
       <c r="D91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B92" t="s">
+        <v>251</v>
+      </c>
+      <c r="C92" t="s">
         <v>252</v>
-      </c>
-      <c r="C92" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B93" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" t="s">
         <v>254</v>
-      </c>
-      <c r="C93" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B94" t="s">
+        <v>255</v>
+      </c>
+      <c r="C94" t="s">
         <v>256</v>
-      </c>
-      <c r="C94" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B95" t="s">
+        <v>257</v>
+      </c>
+      <c r="C95" t="s">
         <v>258</v>
-      </c>
-      <c r="C95" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B97" t="s">
+        <v>259</v>
+      </c>
+      <c r="C97" t="s">
         <v>260</v>
-      </c>
-      <c r="C97" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
+        <v>261</v>
+      </c>
+      <c r="C98" t="s">
         <v>262</v>
-      </c>
-      <c r="C98" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B99" t="s">
+        <v>263</v>
+      </c>
+      <c r="C99" t="s">
         <v>264</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>265</v>
-      </c>
-      <c r="D99" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" t="s">
+        <v>158</v>
+      </c>
+      <c r="C101" t="s">
         <v>159</v>
       </c>
-      <c r="C101" t="s">
-        <v>160</v>
-      </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B102" t="s">
+        <v>268</v>
+      </c>
+      <c r="C102" t="s">
         <v>269</v>
-      </c>
-      <c r="C102" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
+        <v>270</v>
+      </c>
+      <c r="C103" t="s">
         <v>271</v>
-      </c>
-      <c r="C103" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B104" t="s">
+        <v>272</v>
+      </c>
+      <c r="C104" t="s">
         <v>273</v>
-      </c>
-      <c r="C104" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B106" t="s">
+        <v>274</v>
+      </c>
+      <c r="C106" t="s">
         <v>275</v>
-      </c>
-      <c r="C106" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B107" t="s">
+        <v>276</v>
+      </c>
+      <c r="C107" t="s">
         <v>277</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>278</v>
-      </c>
-      <c r="D107" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B108" t="s">
+        <v>276</v>
+      </c>
+      <c r="C108" t="s">
         <v>277</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>278</v>
-      </c>
-      <c r="D108" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B109" t="s">
+        <v>279</v>
+      </c>
+      <c r="C109" t="s">
         <v>280</v>
-      </c>
-      <c r="C109" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B110" t="s">
+        <v>282</v>
+      </c>
+      <c r="C110" t="s">
+        <v>281</v>
+      </c>
+      <c r="D110" t="s">
         <v>283</v>
-      </c>
-      <c r="C110" t="s">
-        <v>282</v>
-      </c>
-      <c r="D110" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Data/PaNET_mapping.xlsx
+++ b/Data/PaNET_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fdp54928/Documents/PaNET-classifier/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fdp54928/Documents/PaNET-classifier/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6D549B-0BE0-6A4A-8310-41A77B9EBD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE647C0-294A-0347-B0BF-59FA0FCB7FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17380" xr2:uid="{88D9EF37-0CDC-9F43-8BAB-2F9D8923655A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="232">
   <si>
     <t>Diffraction</t>
   </si>
@@ -92,9 +92,6 @@
     <t>Knife Edge Scan</t>
   </si>
   <si>
-    <t>Anomalous Diffraction</t>
-  </si>
-  <si>
     <t>Energy Dispersive Diffraction (EDD)</t>
   </si>
   <si>
@@ -107,12 +104,6 @@
     <t>Low Energy Electron Diffraction (LEED)</t>
   </si>
   <si>
-    <t>Multi Wavelength Anomalous Diffraction (MAD)</t>
-  </si>
-  <si>
-    <t>Photo Crystallography</t>
-  </si>
-  <si>
     <t>Photoelectron Diffraction (PhD)</t>
   </si>
   <si>
@@ -143,54 +134,33 @@
     <t>microXRD</t>
   </si>
   <si>
-    <t>Diffracted X-ray Tracking (DXT)</t>
-  </si>
-  <si>
     <t>Soft X-ray Diffraction (SXD)</t>
   </si>
   <si>
     <t>Macromolecular Crystallography (MX)</t>
   </si>
   <si>
-    <t>Serial Femtosecond Crystallography (SFX)</t>
-  </si>
-  <si>
     <t>Serial Synchrotron Crystallography (SSX)</t>
   </si>
   <si>
     <t>Coherent Diffraction Imaging (CDI)</t>
   </si>
   <si>
-    <t>Infrared Nanospectroscopy Imaging</t>
-  </si>
-  <si>
     <t>Phase Contrast Imaging</t>
   </si>
   <si>
     <t>Tomography</t>
   </si>
   <si>
-    <t>UV Circular Dichroism Imaging</t>
-  </si>
-  <si>
     <t>X-ray Fluorescence (XRF)</t>
   </si>
   <si>
-    <t>X-ray Birefringence Imaging (XBI)</t>
-  </si>
-  <si>
     <t>Electron Microscopy (EM)</t>
   </si>
   <si>
-    <t>Infrared Microscopy</t>
-  </si>
-  <si>
     <t>X-ray Microscopy</t>
   </si>
   <si>
-    <t>Anomalous Scattering</t>
-  </si>
-  <si>
     <t>Pair Distribution Function (PDF)</t>
   </si>
   <si>
@@ -254,33 +224,15 @@
     <t>X-ray Photon Correlation Spectroscopy (XPCS)</t>
   </si>
   <si>
-    <t>X-ray Excited Optical Luminescence (XEOL)</t>
-  </si>
-  <si>
     <t>Fragment Screening</t>
   </si>
   <si>
-    <t>In Situ Diffraction</t>
-  </si>
-  <si>
     <t>Long Wavelength Crystallography</t>
   </si>
   <si>
     <t>Micro/nanofocus MX</t>
   </si>
   <si>
-    <t>Molecular Replacement</t>
-  </si>
-  <si>
-    <t>Time Resolved Serial Femtosecond Crystallography (TR-SFX)</t>
-  </si>
-  <si>
-    <t>Fixed Target Serial Synchrotron Crystallography (FT-SSX)</t>
-  </si>
-  <si>
-    <t>Lipidic Cubic Phase Serial Synchrotron Crystallography (LCP-SSX)</t>
-  </si>
-  <si>
     <t>Time Resolved Serial Synchrotron Crystallography (TR-SSX)</t>
   </si>
   <si>
@@ -293,21 +245,12 @@
     <t>Cryo Electron Tomography (Cryo ET)</t>
   </si>
   <si>
-    <t>Magnetic X-ray Tomography (MXT)</t>
-  </si>
-  <si>
     <t>Cryo-soft X-ray Tomography (Cryo-SXT)</t>
   </si>
   <si>
-    <t>Correlative Light Electron Microscopy (CLEM)</t>
-  </si>
-  <si>
     <t>Cryo Electron Microscopy (Cryo EM)</t>
   </si>
   <si>
-    <t>Cryo Focused Ion Beam Scanning Electron Microscopy (FIBSEM)</t>
-  </si>
-  <si>
     <t>PhotoEmmission Electron Microscopy (PEEM)</t>
   </si>
   <si>
@@ -341,9 +284,6 @@
     <t>Grazing Incidence Small Angle Scattering (GISAXS)</t>
   </si>
   <si>
-    <t>Ultra Small Angle X-ray Scattering (USAXS)</t>
-  </si>
-  <si>
     <t>Grazing Incidence Wide Angle Scattering (GIWAXS)</t>
   </si>
   <si>
@@ -353,9 +293,6 @@
     <t>Nano ARPES</t>
   </si>
   <si>
-    <t>UV Synchrotron Radiation Circular Dichroism (SRCD)</t>
-  </si>
-  <si>
     <t>X-ray Magnetic Circular Dichroism (XMCD)</t>
   </si>
   <si>
@@ -368,9 +305,6 @@
     <t>Synchtron-based Fourier Transform Infrared Spectroscopy (SR-FTIR)</t>
   </si>
   <si>
-    <t>Nano Infrared Spectroscopy</t>
-  </si>
-  <si>
     <t>X-ray Magnetic Linear Dichroism (XMLD)</t>
   </si>
   <si>
@@ -428,30 +362,12 @@
     <t>macromolecular crystallography</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01165</t>
-  </si>
-  <si>
-    <t>multi wavelength anomalous diffraction</t>
-  </si>
-  <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01166</t>
-  </si>
-  <si>
-    <t>photo crystallography</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01167</t>
   </si>
   <si>
     <t>photoelectron diffraction</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01168</t>
-  </si>
-  <si>
-    <t>serial femtosecond crystallography</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01169</t>
   </si>
   <si>
@@ -512,12 +428,6 @@
     <t>coherent diffraction imaging</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01175</t>
-  </si>
-  <si>
-    <t>infrared nanospectroscopy imaging</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01116</t>
   </si>
   <si>
@@ -530,48 +440,24 @@
     <t>tomography</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01176</t>
-  </si>
-  <si>
-    <t>UV circular dichroism imaging</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01177</t>
   </si>
   <si>
     <t>x-ray fluorescence</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01327</t>
-  </si>
-  <si>
-    <t>x-ray birefringence imaging</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01145</t>
   </si>
   <si>
     <t>electron microscopy</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01178</t>
-  </si>
-  <si>
-    <t>infrared microscopy</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01180</t>
   </si>
   <si>
     <t>x-ray microscopy</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01049</t>
-  </si>
-  <si>
-    <t>resonant scattering</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01181</t>
   </si>
   <si>
@@ -680,24 +566,12 @@
     <t>x-ray photon correlation spectroscopy</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01140</t>
-  </si>
-  <si>
-    <t>x-ray excited optical luminescence</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01304</t>
   </si>
   <si>
     <t>fragment screening</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01157</t>
-  </si>
-  <si>
-    <t>in-situ diffraction</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01305</t>
   </si>
   <si>
@@ -716,30 +590,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01308</t>
-  </si>
-  <si>
-    <t>molecular replacement</t>
-  </si>
-  <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01309</t>
-  </si>
-  <si>
-    <t>time resolved serial femtosecond crystallography</t>
-  </si>
-  <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01310</t>
-  </si>
-  <si>
-    <t>fixed target serial synchrotron crystallography</t>
-  </si>
-  <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01311</t>
-  </si>
-  <si>
-    <t>lipidic cubic phase serial synchrotron crystallography</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01312</t>
   </si>
   <si>
@@ -791,12 +641,6 @@
     <t>grazing incidence small angle x-ray scattering</t>
   </si>
   <si>
-    <t>http://purl.org/pan-science/PaNET/PaNET01241</t>
-  </si>
-  <si>
-    <t>ultra small angle x-ray scattering</t>
-  </si>
-  <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01316</t>
   </si>
   <si>
@@ -837,9 +681,6 @@
   </si>
   <si>
     <t>The acronym GISAXS is an altLabel.</t>
-  </si>
-  <si>
-    <t>Synonym of the PaNET term.</t>
   </si>
   <si>
     <t>http://purl.org/pan-science/PaNET/PaNET01259</t>
@@ -897,10 +738,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -923,13 +772,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1262,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0A3E7C-0A1C-C647-AA2F-FF37D61C4EDA}">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.6640625" bestFit="1" customWidth="1"/>
@@ -1275,13 +1127,13 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="D1" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1353,16 +1205,22 @@
       <c r="A9" t="s">
         <v>18</v>
       </c>
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1370,195 +1228,201 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>140</v>
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C24" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1566,21 +1430,21 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1588,10 +1452,10 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1599,10 +1463,10 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1610,10 +1474,10 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1621,10 +1485,10 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1632,10 +1496,10 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1643,76 +1507,58 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>48</v>
       </c>
-      <c r="B39" t="s">
-        <v>172</v>
-      </c>
-      <c r="C39" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>49</v>
       </c>
-      <c r="B40" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>52</v>
       </c>
-      <c r="B43" t="s">
-        <v>180</v>
-      </c>
-      <c r="C43" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -1720,10 +1566,10 @@
         <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -1731,10 +1577,10 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -1742,10 +1588,10 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1753,190 +1599,163 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C51" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+      <c r="D55" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>66</v>
       </c>
-      <c r="B57" t="s">
-        <v>202</v>
-      </c>
-      <c r="C57" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>67</v>
       </c>
-      <c r="B58" t="s">
-        <v>204</v>
-      </c>
-      <c r="C58" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>68</v>
       </c>
-      <c r="B59" t="s">
-        <v>206</v>
-      </c>
-      <c r="C59" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="B60" t="s">
-        <v>208</v>
-      </c>
-      <c r="C60" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>70</v>
       </c>
-      <c r="B61" t="s">
-        <v>210</v>
-      </c>
-      <c r="C61" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="C62" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>72</v>
       </c>
-      <c r="B63" t="s">
-        <v>214</v>
-      </c>
-      <c r="C63" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>73</v>
-      </c>
-      <c r="B64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C64" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>74</v>
       </c>
-      <c r="B65" t="s">
-        <v>218</v>
-      </c>
-      <c r="C65" t="s">
-        <v>219</v>
-      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -1944,13 +1763,10 @@
         <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="C67" t="s">
-        <v>223</v>
-      </c>
-      <c r="D67" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -1958,10 +1774,10 @@
         <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="C68" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -1969,32 +1785,29 @@
         <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>229</v>
+        <v>195</v>
+      </c>
+      <c r="D69" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>79</v>
       </c>
-      <c r="B70" t="s">
-        <v>230</v>
-      </c>
-      <c r="C70" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="C71" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -2002,41 +1815,83 @@
         <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="C72" t="s">
-        <v>235</v>
+        <v>200</v>
+      </c>
+      <c r="D72" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>82</v>
       </c>
+      <c r="B73" t="s">
+        <v>201</v>
+      </c>
+      <c r="C73" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>83</v>
       </c>
+      <c r="B74" t="s">
+        <v>203</v>
+      </c>
+      <c r="C74" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>84</v>
       </c>
+      <c r="B75" t="s">
+        <v>205</v>
+      </c>
+      <c r="C75" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>85</v>
       </c>
+      <c r="B76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C76" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>86</v>
       </c>
+      <c r="B77" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>87</v>
       </c>
+      <c r="B78" t="s">
+        <v>211</v>
+      </c>
+      <c r="C78" t="s">
+        <v>212</v>
+      </c>
+      <c r="D78" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
@@ -2047,22 +1902,34 @@
       <c r="A80" t="s">
         <v>89</v>
       </c>
+      <c r="B80" t="s">
+        <v>215</v>
+      </c>
+      <c r="C80" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C81" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>91</v>
       </c>
+      <c r="B82" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
@@ -2073,16 +1940,25 @@
       <c r="A84" t="s">
         <v>93</v>
       </c>
+      <c r="B84" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C85" t="s">
-        <v>237</v>
+        <v>224</v>
+      </c>
+      <c r="D85" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -2090,10 +1966,13 @@
         <v>95</v>
       </c>
       <c r="B86" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>224</v>
+      </c>
+      <c r="D86" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -2101,10 +1980,10 @@
         <v>96</v>
       </c>
       <c r="B87" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -2112,262 +1991,29 @@
         <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="D88" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>99</v>
-      </c>
-      <c r="B90" t="s">
-        <v>247</v>
-      </c>
-      <c r="C90" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>100</v>
-      </c>
-      <c r="B91" t="s">
-        <v>249</v>
-      </c>
-      <c r="C91" t="s">
-        <v>250</v>
-      </c>
-      <c r="D91" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>101</v>
-      </c>
-      <c r="B92" t="s">
-        <v>251</v>
-      </c>
-      <c r="C92" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>102</v>
-      </c>
-      <c r="B93" t="s">
-        <v>253</v>
-      </c>
-      <c r="C93" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>103</v>
-      </c>
-      <c r="B94" t="s">
-        <v>255</v>
-      </c>
-      <c r="C94" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>104</v>
-      </c>
-      <c r="B95" t="s">
-        <v>257</v>
-      </c>
-      <c r="C95" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B97" t="s">
-        <v>259</v>
-      </c>
-      <c r="C97" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>107</v>
-      </c>
-      <c r="B98" t="s">
-        <v>261</v>
-      </c>
-      <c r="C98" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>108</v>
-      </c>
-      <c r="B99" t="s">
-        <v>263</v>
-      </c>
-      <c r="C99" t="s">
-        <v>264</v>
-      </c>
-      <c r="D99" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>110</v>
-      </c>
-      <c r="B101" t="s">
-        <v>158</v>
-      </c>
-      <c r="C101" t="s">
-        <v>159</v>
-      </c>
-      <c r="D101" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>111</v>
-      </c>
-      <c r="B102" t="s">
-        <v>268</v>
-      </c>
-      <c r="C102" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>112</v>
-      </c>
-      <c r="B103" t="s">
-        <v>270</v>
-      </c>
-      <c r="C103" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>113</v>
-      </c>
-      <c r="B104" t="s">
-        <v>272</v>
-      </c>
-      <c r="C104" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>115</v>
-      </c>
-      <c r="B106" t="s">
-        <v>274</v>
-      </c>
-      <c r="C106" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>116</v>
-      </c>
-      <c r="B107" t="s">
-        <v>276</v>
-      </c>
-      <c r="C107" t="s">
-        <v>277</v>
-      </c>
-      <c r="D107" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>117</v>
-      </c>
-      <c r="B108" t="s">
-        <v>276</v>
-      </c>
-      <c r="C108" t="s">
-        <v>277</v>
-      </c>
-      <c r="D108" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>118</v>
-      </c>
-      <c r="B109" t="s">
-        <v>279</v>
-      </c>
-      <c r="C109" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>119</v>
-      </c>
-      <c r="B110" t="s">
-        <v>282</v>
-      </c>
-      <c r="C110" t="s">
-        <v>281</v>
-      </c>
-      <c r="D110" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B20" r:id="rId1" xr:uid="{F26C5E2B-4923-0B4D-B3FD-2BC530732EA0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>